--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleTransferInfoTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleTransferInfoTemplate.xlsx
@@ -1,196 +1,87 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>WPS 表格</Application>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>pc</dc:creator>
+  <cp:lastModifiedBy>风趣</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2025-08-22T01:37:00Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2025-10-28T10:23:29Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
+    <vt:lpwstr>2680EEF296B64AAC9138A8EC06B50379_13</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
+    <vt:lpwstr>2052-12.1.0.23125</vt:lpwstr>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>序号</t>
-    </r>
+    <t>*序号</t>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>转移日期</t>
-    </r>
+    <t>*转移日期</t>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>转入人</t>
-    </r>
+    <t>*转移类型</t>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>转入部门</t>
-    </r>
+    <t>*转入人</t>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>转出人</t>
-    </r>
+    <t>*转入部门</t>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>转出部门</t>
-    </r>
+    <t>*转出人</t>
+  </si>
+  <si>
+    <t>*转出部门</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SKU</t>
-    </r>
+    <t>*SKU</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>使用方</t>
-    </r>
+    <t>*原使用方</t>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>转移数量</t>
-    </r>
+    <t>*目标使用方</t>
+  </si>
+  <si>
+    <t>*转移数量</t>
   </si>
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -1090,7 +981,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
     <a:clrScheme name="WPS">
@@ -1337,24 +1228,53 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="22560" windowHeight="11120"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.7272727272727" customWidth="1"/>
     <col min="2" max="2" width="20.0909090909091" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="6" width="17.8181818181818" customWidth="1"/>
-    <col min="7" max="7" width="17.7272727272727" customWidth="1"/>
-    <col min="8" max="9" width="15.5454545454545" customWidth="1"/>
-    <col min="10" max="10" width="17.8181818181818" customWidth="1"/>
-    <col min="11" max="11" width="19.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="7" width="17.8181818181818" customWidth="1"/>
+    <col min="8" max="8" width="15.5454545454545" customWidth="1"/>
+    <col min="9" max="9" width="15.5454545454545" customWidth="1"/>
+    <col min="10" max="11" width="17.8181818181818" customWidth="1"/>
+    <col min="12" max="12" width="17.7272727272727" customWidth="1"/>
+    <col min="13" max="13" width="19.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1373,7 +1293,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1385,8 +1305,14 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>6</v>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
